--- a/public/assets/templates/maintenance/refrigerasi.xlsx
+++ b/public/assets/templates/maintenance/refrigerasi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Documents\MAGANG\PT BAS\ENG\Maintenance\Template Laporan Form\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99A37FC0-4E38-4FFF-BA3D-439086477B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0F9816-8978-4E20-8810-CDE8857BBBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{BD070262-A742-4FD6-B71B-7736A1293F38}"/>
   </bookViews>
@@ -662,40 +662,250 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -704,213 +914,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1282,637 +1285,637 @@
   <dimension ref="A1:K59"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="81" customWidth="1"/>
-    <col min="2" max="2" width="3" style="81" customWidth="1"/>
-    <col min="3" max="3" width="23" style="81" customWidth="1"/>
-    <col min="4" max="4" width="6.26953125" style="81" customWidth="1"/>
-    <col min="5" max="5" width="2.26953125" style="81" customWidth="1"/>
-    <col min="6" max="6" width="15.26953125" style="81" customWidth="1"/>
-    <col min="7" max="7" width="2.7265625" style="81" customWidth="1"/>
-    <col min="8" max="8" width="5.26953125" style="81" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="3" style="17" customWidth="1"/>
+    <col min="3" max="3" width="23" style="17" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" style="17" customWidth="1"/>
+    <col min="5" max="5" width="2.26953125" style="17" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="2.7265625" style="17" customWidth="1"/>
+    <col min="8" max="8" width="5.26953125" style="17" customWidth="1"/>
     <col min="12" max="12" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickTop="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="78"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7" t="s">
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="80"/>
     </row>
     <row r="3" spans="1:11" ht="10.75" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="12" t="s">
+      <c r="E3" s="81"/>
+      <c r="F3" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="83"/>
     </row>
     <row r="4" spans="1:11" ht="10.75" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="12" t="s">
+      <c r="E4" s="81"/>
+      <c r="F4" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:11" s="20" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A5" s="14" t="s">
+      <c r="G4" s="82"/>
+      <c r="H4" s="83"/>
+    </row>
+    <row r="5" spans="1:11" s="5" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16" t="s">
+      <c r="C5" s="70"/>
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
-    </row>
-    <row r="6" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="71"/>
+    </row>
+    <row r="6" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A6" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="23" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="25"/>
-    </row>
-    <row r="7" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="23" t="s">
+      <c r="D6" s="8"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="61"/>
+    </row>
+    <row r="7" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A7" s="72"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="25"/>
-    </row>
-    <row r="8" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A8" s="21"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="23" t="s">
+      <c r="D7" s="8"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="61"/>
+    </row>
+    <row r="8" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A8" s="72"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="25"/>
-    </row>
-    <row r="9" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23" t="s">
+      <c r="D8" s="8"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="61"/>
+    </row>
+    <row r="9" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A9" s="72"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="25"/>
-    </row>
-    <row r="10" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="23" t="s">
+      <c r="D9" s="8"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="61"/>
+    </row>
+    <row r="10" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A10" s="72"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="25"/>
-    </row>
-    <row r="11" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A11" s="21"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="23" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="61"/>
+    </row>
+    <row r="11" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A11" s="72"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="25"/>
-    </row>
-    <row r="12" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="27" t="s">
+      <c r="D11" s="8"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="61"/>
+    </row>
+    <row r="12" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A12" s="72"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="25"/>
-      <c r="K12" s="28"/>
-    </row>
-    <row r="13" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A13" s="21"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="23" t="s">
+      <c r="D12" s="8"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="61"/>
+      <c r="K12" s="69"/>
+    </row>
+    <row r="13" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A13" s="72"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="25"/>
-      <c r="K13" s="28"/>
-    </row>
-    <row r="14" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A14" s="21"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23" t="s">
+      <c r="D13" s="8"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="61"/>
+      <c r="K13" s="69"/>
+    </row>
+    <row r="14" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A14" s="72"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="25"/>
-      <c r="K14" s="28"/>
-    </row>
-    <row r="15" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A15" s="21"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23" t="s">
+      <c r="D14" s="8"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="61"/>
+      <c r="K14" s="69"/>
+    </row>
+    <row r="15" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A15" s="72"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="25"/>
-      <c r="K15" s="28"/>
-    </row>
-    <row r="16" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A16" s="21"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="27" t="s">
+      <c r="D15" s="8"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="61"/>
+      <c r="K15" s="69"/>
+    </row>
+    <row r="16" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A16" s="72"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="22"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="25"/>
-      <c r="K16" s="28"/>
-    </row>
-    <row r="17" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A17" s="21"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="25"/>
-      <c r="K17" s="28"/>
-    </row>
-    <row r="18" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A18" s="21"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="25"/>
-      <c r="K18" s="28"/>
-    </row>
-    <row r="19" spans="1:11" s="31" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A19" s="30" t="s">
+      <c r="D16" s="8"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="61"/>
+      <c r="K16" s="69"/>
+    </row>
+    <row r="17" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A17" s="72"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="61"/>
+      <c r="K17" s="69"/>
+    </row>
+    <row r="18" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A18" s="72"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="61"/>
+      <c r="K18" s="69"/>
+    </row>
+    <row r="19" spans="1:11" s="12" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A19" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="25"/>
-      <c r="K19" s="28"/>
-    </row>
-    <row r="20" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A20" s="30"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="23" t="s">
+      <c r="D19" s="8"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="61"/>
+      <c r="K19" s="69"/>
+    </row>
+    <row r="20" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A20" s="68"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="25"/>
-      <c r="K20" s="28"/>
-    </row>
-    <row r="21" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A21" s="30"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="23" t="s">
+      <c r="D20" s="8"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="61"/>
+      <c r="K20" s="69"/>
+    </row>
+    <row r="21" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A21" s="68"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="25"/>
-      <c r="K21" s="28"/>
-    </row>
-    <row r="22" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A22" s="30"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="23" t="s">
+      <c r="D21" s="8"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="61"/>
+      <c r="K21" s="69"/>
+    </row>
+    <row r="22" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A22" s="68"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="22"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="25"/>
-      <c r="K22" s="28"/>
-    </row>
-    <row r="23" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A23" s="30"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="23" t="s">
+      <c r="D22" s="8"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="61"/>
+      <c r="K22" s="69"/>
+    </row>
+    <row r="23" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A23" s="68"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="22"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="25"/>
-      <c r="K23" s="32"/>
-    </row>
-    <row r="24" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A24" s="30"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23" t="s">
+      <c r="D23" s="8"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="61"/>
+      <c r="K23" s="59"/>
+    </row>
+    <row r="24" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A24" s="68"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="25"/>
-      <c r="K24" s="32"/>
-    </row>
-    <row r="25" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A25" s="30"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="25"/>
-      <c r="K25" s="32"/>
-    </row>
-    <row r="26" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A26" s="30"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="25"/>
-      <c r="K26" s="32"/>
-    </row>
-    <row r="27" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A27" s="33" t="s">
+      <c r="D24" s="8"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="61"/>
+      <c r="K24" s="59"/>
+    </row>
+    <row r="25" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A25" s="68"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="61"/>
+      <c r="K25" s="59"/>
+    </row>
+    <row r="26" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A26" s="68"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="61"/>
+      <c r="K26" s="59"/>
+    </row>
+    <row r="27" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A27" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="34" t="s">
+      <c r="B27" s="6"/>
+      <c r="C27" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="22"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="37"/>
-      <c r="K27" s="32"/>
-    </row>
-    <row r="28" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A28" s="38"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="34" t="s">
+      <c r="D27" s="8"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="67"/>
+      <c r="K27" s="59"/>
+    </row>
+    <row r="28" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A28" s="63"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="22"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="37"/>
-      <c r="K28" s="32"/>
-    </row>
-    <row r="29" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A29" s="38"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="34" t="s">
+      <c r="D28" s="8"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="67"/>
+      <c r="K28" s="59"/>
+    </row>
+    <row r="29" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A29" s="63"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="22"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="37"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="32"/>
-    </row>
-    <row r="30" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A30" s="38"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="37"/>
-      <c r="K30" s="32"/>
-    </row>
-    <row r="31" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A31" s="40"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="37"/>
-    </row>
-    <row r="32" spans="1:11" s="26" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A32" s="41"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="43"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="67"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="59"/>
+    </row>
+    <row r="30" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A30" s="63"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="66"/>
+      <c r="H30" s="67"/>
+      <c r="K30" s="59"/>
+    </row>
+    <row r="31" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A31" s="64"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="66"/>
+      <c r="G31" s="66"/>
+      <c r="H31" s="67"/>
+    </row>
+    <row r="32" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A32" s="42"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="44"/>
     </row>
     <row r="33" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="47" t="s">
+      <c r="B33" s="46"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="48"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
     </row>
     <row r="34" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A34" s="49"/>
-      <c r="B34" s="50"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="17" t="s">
+      <c r="A34" s="48"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="53" t="s">
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="15" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A35" s="49"/>
-      <c r="B35" s="50"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="53"/>
+      <c r="A35" s="48"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="15"/>
     </row>
     <row r="36" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A36" s="49"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="53"/>
+      <c r="A36" s="48"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="15"/>
     </row>
     <row r="37" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A37" s="49"/>
-      <c r="B37" s="50"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="57"/>
+      <c r="A37" s="48"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="16"/>
     </row>
     <row r="38" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A38" s="49"/>
-      <c r="B38" s="50"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="57"/>
+      <c r="A38" s="48"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="16"/>
     </row>
     <row r="39" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A39" s="49"/>
-      <c r="B39" s="50"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="57"/>
+      <c r="A39" s="48"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A40" s="49"/>
-      <c r="B40" s="50"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="57"/>
+      <c r="A40" s="48"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A41" s="49"/>
-      <c r="B41" s="50"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="57"/>
+      <c r="A41" s="48"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="50"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="16"/>
     </row>
     <row r="42" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A42" s="49"/>
-      <c r="B42" s="50"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="54"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="55"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="57"/>
+      <c r="A42" s="48"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="50"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A43" s="49"/>
-      <c r="B43" s="50"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="54"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="57"/>
+      <c r="A43" s="48"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="16"/>
     </row>
     <row r="44" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A44" s="49"/>
-      <c r="B44" s="50"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="57"/>
+      <c r="A44" s="48"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="50"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A45" s="49"/>
-      <c r="B45" s="50"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="60" t="s">
+      <c r="A45" s="48"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="50"/>
+      <c r="D45" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="E45" s="61"/>
-      <c r="F45" s="62"/>
-      <c r="G45" s="63"/>
-      <c r="H45" s="64"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="23"/>
     </row>
     <row r="46" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A46" s="49"/>
-      <c r="B46" s="50"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="65" t="s">
+      <c r="A46" s="48"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="50"/>
+      <c r="D46" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="E46" s="66"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="68"/>
-      <c r="H46" s="69"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="25"/>
     </row>
     <row r="47" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A47" s="49"/>
-      <c r="B47" s="50"/>
-      <c r="C47" s="51"/>
-      <c r="D47" s="70" t="s">
+      <c r="A47" s="48"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="50"/>
+      <c r="D47" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E47" s="71"/>
-      <c r="F47" s="72"/>
-      <c r="G47" s="63"/>
-      <c r="H47" s="64"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="23"/>
     </row>
     <row r="48" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A48" s="49"/>
-      <c r="B48" s="50"/>
-      <c r="C48" s="51"/>
-      <c r="D48" s="65" t="s">
+      <c r="A48" s="48"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="50"/>
+      <c r="D48" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="E48" s="66"/>
-      <c r="F48" s="67"/>
-      <c r="G48" s="68"/>
-      <c r="H48" s="69"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="25"/>
     </row>
     <row r="49" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A49" s="49"/>
-      <c r="B49" s="50"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="71" t="s">
+      <c r="A49" s="48"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E49" s="71"/>
-      <c r="F49" s="72"/>
-      <c r="G49" s="63"/>
-      <c r="H49" s="64"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="23"/>
     </row>
     <row r="50" spans="1:8" ht="10.75" customHeight="1" thickBot="1">
-      <c r="A50" s="73"/>
-      <c r="B50" s="74"/>
-      <c r="C50" s="75"/>
-      <c r="D50" s="76" t="s">
+      <c r="A50" s="51"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E50" s="77"/>
-      <c r="F50" s="78"/>
-      <c r="G50" s="79"/>
-      <c r="H50" s="80"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="30"/>
     </row>
     <row r="51" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F51" s="82" t="s">
+      <c r="F51" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="G51" s="82"/>
-      <c r="H51" s="82"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
     </row>
     <row r="52" spans="1:8" ht="9" customHeight="1">
       <c r="A52"/>
@@ -1996,30 +1999,30 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="G47:H48"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D43:G43"/>
-    <mergeCell ref="D44:G44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="G45:H46"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A33:C50"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="D38:G38"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A6:A18"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="K12:K22"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="E18:H18"/>
     <mergeCell ref="K23:K30"/>
     <mergeCell ref="E24:H24"/>
     <mergeCell ref="E25:H25"/>
@@ -2036,30 +2039,30 @@
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="E22:H22"/>
     <mergeCell ref="E23:H23"/>
-    <mergeCell ref="K12:K22"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A6:A18"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:C50"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="D44:G44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="G45:H46"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="G47:H48"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="D50:F50"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.195138888888889" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/refrigerasi.xlsx
+++ b/public/assets/templates/maintenance/refrigerasi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0F9816-8978-4E20-8810-CDE8857BBBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302B8DCA-DB62-456F-B3D4-02A94F6D12CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{BD070262-A742-4FD6-B71B-7736A1293F38}"/>
   </bookViews>
@@ -36,10 +36,6 @@
     <t>PT BUMI ALAM SEGAR</t>
   </si>
   <si>
-    <t xml:space="preserve">Tanggal 
-</t>
-  </si>
-  <si>
     <t>:</t>
   </si>
   <si>
@@ -164,6 +160,9 @@
   </si>
   <si>
     <t>FRM/EUT/01/009/005-02</t>
+  </si>
+  <si>
+    <t>Tanggal</t>
   </si>
 </sst>
 </file>
@@ -717,6 +716,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -741,15 +749,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -765,6 +764,57 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -789,57 +839,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -882,6 +881,15 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -905,15 +913,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1297,90 +1296,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickTop="1">
-      <c r="A1" s="73"/>
-      <c r="B1" s="74"/>
-      <c r="C1" s="77" t="s">
+      <c r="A1" s="76"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="78"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="81"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="75"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="79" t="s">
+      <c r="A2" s="78"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="80"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="83"/>
     </row>
     <row r="3" spans="1:11" ht="10.75" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="82" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="82"/>
-      <c r="H3" s="83"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="74"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:11" ht="10.75" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="81" t="s">
+      <c r="E4" s="73"/>
+      <c r="F4" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="81"/>
-      <c r="F4" s="82" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="82"/>
-      <c r="H4" s="83"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="75"/>
     </row>
     <row r="5" spans="1:11" s="5" customFormat="1" ht="10.75" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="70" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" s="70" t="s">
-        <v>9</v>
       </c>
       <c r="C5" s="70"/>
       <c r="D5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
       <c r="H5" s="71"/>
     </row>
     <row r="6" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
       <c r="A6" s="72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="60"/>
@@ -1392,7 +1391,7 @@
       <c r="A7" s="72"/>
       <c r="B7" s="6"/>
       <c r="C7" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="60"/>
@@ -1404,7 +1403,7 @@
       <c r="A8" s="72"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="60"/>
@@ -1416,7 +1415,7 @@
       <c r="A9" s="72"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="60"/>
@@ -1428,7 +1427,7 @@
       <c r="A10" s="72"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="60"/>
@@ -1440,7 +1439,7 @@
       <c r="A11" s="72"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="60"/>
@@ -1452,7 +1451,7 @@
       <c r="A12" s="72"/>
       <c r="B12" s="6"/>
       <c r="C12" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="60"/>
@@ -1465,7 +1464,7 @@
       <c r="A13" s="72"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="60"/>
@@ -1478,7 +1477,7 @@
       <c r="A14" s="72"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="60"/>
@@ -1491,7 +1490,7 @@
       <c r="A15" s="72"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="60"/>
@@ -1504,7 +1503,7 @@
       <c r="A16" s="72"/>
       <c r="B16" s="6"/>
       <c r="C16" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="60"/>
@@ -1537,11 +1536,11 @@
     </row>
     <row r="19" spans="1:11" s="12" customFormat="1" ht="10.75" customHeight="1">
       <c r="A19" s="68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="60"/>
@@ -1554,7 +1553,7 @@
       <c r="A20" s="68"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="60"/>
@@ -1567,7 +1566,7 @@
       <c r="A21" s="68"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="60"/>
@@ -1580,7 +1579,7 @@
       <c r="A22" s="68"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="60"/>
@@ -1593,7 +1592,7 @@
       <c r="A23" s="68"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="60"/>
@@ -1606,7 +1605,7 @@
       <c r="A24" s="68"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="60"/>
@@ -1639,11 +1638,11 @@
     </row>
     <row r="27" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
       <c r="A27" s="62" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="65"/>
@@ -1656,7 +1655,7 @@
       <c r="A28" s="63"/>
       <c r="B28" s="6"/>
       <c r="C28" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="65"/>
@@ -1669,7 +1668,7 @@
       <c r="A29" s="63"/>
       <c r="B29" s="6"/>
       <c r="C29" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="65"/>
@@ -1701,209 +1700,209 @@
       <c r="H31" s="67"/>
     </row>
     <row r="32" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A32" s="42"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="44"/>
+      <c r="A32" s="34"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="36"/>
     </row>
     <row r="33" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A33" s="45" t="s">
+      <c r="A33" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="38"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="46"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="54" t="s">
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="47"/>
+    </row>
+    <row r="34" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A34" s="40"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="55"/>
-    </row>
-    <row r="34" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A34" s="48"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="56" t="s">
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="57"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="15" t="s">
+    </row>
+    <row r="35" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A35" s="40"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="15"/>
+    </row>
+    <row r="36" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A36" s="40"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="15"/>
+    </row>
+    <row r="37" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A37" s="40"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="16"/>
+    </row>
+    <row r="38" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A38" s="40"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="16"/>
+    </row>
+    <row r="39" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A39" s="40"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="16"/>
+    </row>
+    <row r="40" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A40" s="40"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="16"/>
+    </row>
+    <row r="41" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A41" s="40"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="16"/>
+    </row>
+    <row r="42" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A42" s="40"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="16"/>
+    </row>
+    <row r="43" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A43" s="40"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="16"/>
+    </row>
+    <row r="44" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A44" s="40"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="16"/>
+    </row>
+    <row r="45" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A45" s="40"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="56" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A35" s="48"/>
-      <c r="B35" s="49"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="15"/>
-    </row>
-    <row r="36" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A36" s="48"/>
-      <c r="B36" s="49"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="35"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="15"/>
-    </row>
-    <row r="37" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A37" s="48"/>
-      <c r="B37" s="49"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="16"/>
-    </row>
-    <row r="38" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A38" s="48"/>
-      <c r="B38" s="49"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="16"/>
-    </row>
-    <row r="39" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A39" s="48"/>
-      <c r="B39" s="49"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="16"/>
-    </row>
-    <row r="40" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A40" s="48"/>
-      <c r="B40" s="49"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="16"/>
-    </row>
-    <row r="41" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A41" s="48"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="50"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="16"/>
-    </row>
-    <row r="42" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A42" s="48"/>
-      <c r="B42" s="49"/>
-      <c r="C42" s="50"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="16"/>
-    </row>
-    <row r="43" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A43" s="48"/>
-      <c r="B43" s="49"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="16"/>
-    </row>
-    <row r="44" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A44" s="48"/>
-      <c r="B44" s="49"/>
-      <c r="C44" s="50"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="16"/>
-    </row>
-    <row r="45" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A45" s="48"/>
-      <c r="B45" s="49"/>
-      <c r="C45" s="50"/>
-      <c r="D45" s="39" t="s">
+      <c r="E45" s="57"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="26"/>
+    </row>
+    <row r="46" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A46" s="40"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E45" s="40"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="23"/>
-    </row>
-    <row r="46" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A46" s="48"/>
-      <c r="B46" s="49"/>
-      <c r="C46" s="50"/>
-      <c r="D46" s="26" t="s">
+      <c r="E46" s="19"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="28"/>
+    </row>
+    <row r="47" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A47" s="40"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="E46" s="27"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="25"/>
-    </row>
-    <row r="47" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A47" s="48"/>
-      <c r="B47" s="49"/>
-      <c r="C47" s="50"/>
-      <c r="D47" s="19" t="s">
+      <c r="E47" s="23"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="26"/>
+    </row>
+    <row r="48" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A48" s="40"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="E47" s="20"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="23"/>
-    </row>
-    <row r="48" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A48" s="48"/>
-      <c r="B48" s="49"/>
-      <c r="C48" s="50"/>
-      <c r="D48" s="26" t="s">
+      <c r="E48" s="19"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="28"/>
+    </row>
+    <row r="49" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A49" s="40"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E48" s="27"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="25"/>
-    </row>
-    <row r="49" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A49" s="48"/>
-      <c r="B49" s="49"/>
-      <c r="C49" s="50"/>
-      <c r="D49" s="20" t="s">
+      <c r="E49" s="23"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="26"/>
+    </row>
+    <row r="50" spans="1:8" ht="10.75" customHeight="1" thickBot="1">
+      <c r="A50" s="43"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="31" t="s">
         <v>42</v>
-      </c>
-      <c r="E49" s="20"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="23"/>
-    </row>
-    <row r="50" spans="1:8" ht="10.75" customHeight="1" thickBot="1">
-      <c r="A50" s="51"/>
-      <c r="B50" s="52"/>
-      <c r="C50" s="53"/>
-      <c r="D50" s="31" t="s">
-        <v>43</v>
       </c>
       <c r="E50" s="32"/>
       <c r="F50" s="33"/>
@@ -1911,11 +1910,11 @@
       <c r="H50" s="30"/>
     </row>
     <row r="51" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F51" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
+      <c r="F51" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
     </row>
     <row r="52" spans="1:8" ht="9" customHeight="1">
       <c r="A52"/>

--- a/public/assets/templates/maintenance/refrigerasi.xlsx
+++ b/public/assets/templates/maintenance/refrigerasi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302B8DCA-DB62-456F-B3D4-02A94F6D12CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8502E5CA-AFC8-42F9-8C73-F862A582E721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{BD070262-A742-4FD6-B71B-7736A1293F38}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="REFRIGASI" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">REFRIGASI!$A$1:$H$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">REFRIGASI!$A$1:$H$53</definedName>
   </definedNames>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
   <si>
     <t>LAPORAN MAINTENANCE REFRIGERASI</t>
   </si>
@@ -163,6 +163,21 @@
   </si>
   <si>
     <t>Tanggal</t>
+  </si>
+  <si>
+    <t>Waktu Mulai</t>
+  </si>
+  <si>
+    <t>Waktu Selesai</t>
+  </si>
+  <si>
+    <t>Kode Mesin</t>
+  </si>
+  <si>
+    <t>Lokasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">: </t>
   </si>
 </sst>
 </file>
@@ -716,6 +731,168 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -737,18 +914,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -763,156 +928,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1281,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F8696F-2901-4BD1-A6F5-A5CC04A662FE}">
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.81640625" style="17" customWidth="1"/>
@@ -1296,28 +1311,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickTop="1">
-      <c r="A1" s="76"/>
-      <c r="B1" s="77"/>
-      <c r="C1" s="80" t="s">
+      <c r="A1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="81"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="78"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="82" t="s">
+      <c r="A2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="83"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:11" ht="10.75" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -1327,616 +1342,632 @@
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="73"/>
-      <c r="F3" s="74" t="s">
+      <c r="E3" s="18"/>
+      <c r="F3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="74"/>
-      <c r="H3" s="75"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="20"/>
     </row>
     <row r="4" spans="1:11" ht="10.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="73" t="s">
+      <c r="D4" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="F4" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
+    </row>
+    <row r="5" spans="1:11" ht="10.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="20"/>
+    </row>
+    <row r="6" spans="1:11" ht="10.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="73"/>
-      <c r="F4" s="74" t="s">
+      <c r="E6" s="18"/>
+      <c r="F6" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="74"/>
-      <c r="H4" s="75"/>
-    </row>
-    <row r="5" spans="1:11" s="5" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A5" s="3" t="s">
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
+    </row>
+    <row r="7" spans="1:11" s="5" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B7" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="70"/>
-      <c r="D5" s="4" t="s">
+      <c r="C7" s="29"/>
+      <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="48" t="s">
+      <c r="E7" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="71"/>
-    </row>
-    <row r="6" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A6" s="72" t="s">
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="32"/>
+    </row>
+    <row r="8" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A8" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="61"/>
-    </row>
-    <row r="7" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A7" s="72"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="61"/>
-    </row>
-    <row r="8" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A8" s="72"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" s="8"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="61"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="35"/>
     </row>
     <row r="9" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A9" s="72"/>
+      <c r="A9" s="33"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D9" s="8"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="61"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="35"/>
     </row>
     <row r="10" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A10" s="72"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D10" s="8"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="61"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="35"/>
     </row>
     <row r="11" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A11" s="72"/>
+      <c r="A11" s="33"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="61"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="35"/>
     </row>
     <row r="12" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A12" s="72"/>
+      <c r="A12" s="33"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="10" t="s">
-        <v>18</v>
+      <c r="C12" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="D12" s="8"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="61"/>
-      <c r="K12" s="69"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A13" s="72"/>
+      <c r="A13" s="33"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" s="8"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="61"/>
-      <c r="K13" s="69"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
     </row>
     <row r="14" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A14" s="72"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="6"/>
-      <c r="C14" s="7" t="s">
-        <v>20</v>
+      <c r="C14" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="D14" s="8"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="61"/>
-      <c r="K14" s="69"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="35"/>
+      <c r="K14" s="36"/>
     </row>
     <row r="15" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A15" s="72"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="35"/>
+      <c r="K15" s="36"/>
+    </row>
+    <row r="16" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A16" s="33"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="35"/>
+      <c r="K16" s="36"/>
+    </row>
+    <row r="17" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A17" s="33"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="61"/>
-      <c r="K15" s="69"/>
-    </row>
-    <row r="16" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A16" s="72"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="10" t="s">
+      <c r="D17" s="8"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="35"/>
+      <c r="K17" s="36"/>
+    </row>
+    <row r="18" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A18" s="33"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="61"/>
-      <c r="K16" s="69"/>
-    </row>
-    <row r="17" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A17" s="72"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="61"/>
-      <c r="K17" s="69"/>
-    </row>
-    <row r="18" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A18" s="72"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="11"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="61"/>
-      <c r="K18" s="69"/>
-    </row>
-    <row r="19" spans="1:11" s="12" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A19" s="68" t="s">
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="35"/>
+      <c r="K18" s="36"/>
+    </row>
+    <row r="19" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A19" s="33"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="35"/>
+      <c r="K19" s="36"/>
+    </row>
+    <row r="20" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A20" s="33"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="35"/>
+      <c r="K20" s="36"/>
+    </row>
+    <row r="21" spans="1:11" s="12" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A21" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="61"/>
-      <c r="K19" s="69"/>
-    </row>
-    <row r="20" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A20" s="68"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="61"/>
-      <c r="K20" s="69"/>
-    </row>
-    <row r="21" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A21" s="68"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="8"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="61"/>
-      <c r="K21" s="69"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="35"/>
+      <c r="K21" s="36"/>
     </row>
     <row r="22" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A22" s="68"/>
+      <c r="A22" s="44"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D22" s="8"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="61"/>
-      <c r="K22" s="69"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="35"/>
+      <c r="K22" s="36"/>
     </row>
     <row r="23" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A23" s="68"/>
+      <c r="A23" s="44"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D23" s="8"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="61"/>
-      <c r="K23" s="59"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="35"/>
+      <c r="K23" s="36"/>
     </row>
     <row r="24" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A24" s="68"/>
+      <c r="A24" s="44"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="35"/>
+      <c r="K24" s="36"/>
+    </row>
+    <row r="25" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A25" s="44"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="35"/>
+      <c r="K25" s="37"/>
+    </row>
+    <row r="26" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A26" s="44"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="61"/>
-      <c r="K24" s="59"/>
-    </row>
-    <row r="25" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A25" s="68"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="60"/>
-      <c r="G25" s="60"/>
-      <c r="H25" s="61"/>
-      <c r="K25" s="59"/>
-    </row>
-    <row r="26" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A26" s="68"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="11"/>
       <c r="D26" s="8"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="61"/>
-      <c r="K26" s="59"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="35"/>
+      <c r="K26" s="37"/>
     </row>
     <row r="27" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A27" s="62" t="s">
+      <c r="A27" s="44"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="35"/>
+      <c r="K27" s="37"/>
+    </row>
+    <row r="28" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A28" s="44"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="35"/>
+      <c r="K28" s="37"/>
+    </row>
+    <row r="29" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A29" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="67"/>
-      <c r="K27" s="59"/>
-    </row>
-    <row r="28" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A28" s="63"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="67"/>
-      <c r="K28" s="59"/>
-    </row>
-    <row r="29" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A29" s="63"/>
       <c r="B29" s="6"/>
       <c r="C29" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="43"/>
+      <c r="K29" s="37"/>
+    </row>
+    <row r="30" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A30" s="39"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="8"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="43"/>
+      <c r="K30" s="37"/>
+    </row>
+    <row r="31" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A31" s="39"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="66"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="67"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="59"/>
-    </row>
-    <row r="30" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A30" s="63"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="65"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="66"/>
-      <c r="H30" s="67"/>
-      <c r="K30" s="59"/>
-    </row>
-    <row r="31" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A31" s="64"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="10"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="66"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="67"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="43"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="37"/>
     </row>
     <row r="32" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A32" s="34"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="36"/>
-    </row>
-    <row r="33" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A33" s="37" t="s">
+      <c r="A32" s="39"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="43"/>
+      <c r="K32" s="37"/>
+    </row>
+    <row r="33" spans="1:8" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A33" s="40"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="43"/>
+    </row>
+    <row r="34" spans="1:8" s="9" customFormat="1" ht="10.75" customHeight="1">
+      <c r="A34" s="45"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="47"/>
+    </row>
+    <row r="35" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A35" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="46" t="s">
+      <c r="B35" s="49"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="47"/>
-    </row>
-    <row r="34" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A34" s="40"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="48" t="s">
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="58"/>
+    </row>
+    <row r="36" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A36" s="51"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="15" t="s">
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A35" s="40"/>
-      <c r="B35" s="41"/>
-      <c r="C35" s="42"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="15"/>
-    </row>
-    <row r="36" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A36" s="40"/>
-      <c r="B36" s="41"/>
-      <c r="C36" s="42"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="53"/>
-      <c r="H36" s="15"/>
-    </row>
     <row r="37" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A37" s="40"/>
-      <c r="B37" s="41"/>
-      <c r="C37" s="42"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="16"/>
+      <c r="A37" s="51"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="62"/>
+      <c r="H37" s="15"/>
     </row>
     <row r="38" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A38" s="40"/>
-      <c r="B38" s="41"/>
-      <c r="C38" s="42"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="53"/>
-      <c r="H38" s="16"/>
+      <c r="A38" s="51"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="15"/>
     </row>
     <row r="39" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A39" s="40"/>
-      <c r="B39" s="41"/>
-      <c r="C39" s="42"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="53"/>
+      <c r="A39" s="51"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="62"/>
       <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A40" s="40"/>
-      <c r="B40" s="41"/>
-      <c r="C40" s="42"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="53"/>
+      <c r="A40" s="51"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="62"/>
       <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A41" s="40"/>
-      <c r="B41" s="41"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="53"/>
+      <c r="A41" s="51"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="61"/>
+      <c r="G41" s="62"/>
       <c r="H41" s="16"/>
     </row>
     <row r="42" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A42" s="40"/>
-      <c r="B42" s="41"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="53"/>
+      <c r="A42" s="51"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="61"/>
+      <c r="G42" s="62"/>
       <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A43" s="40"/>
-      <c r="B43" s="41"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="53"/>
+      <c r="A43" s="51"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="53"/>
+      <c r="D43" s="60"/>
+      <c r="E43" s="61"/>
+      <c r="F43" s="61"/>
+      <c r="G43" s="62"/>
       <c r="H43" s="16"/>
     </row>
     <row r="44" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A44" s="40"/>
-      <c r="B44" s="41"/>
-      <c r="C44" s="42"/>
-      <c r="D44" s="54"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="53"/>
+      <c r="A44" s="51"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="60"/>
+      <c r="E44" s="61"/>
+      <c r="F44" s="61"/>
+      <c r="G44" s="62"/>
       <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A45" s="40"/>
-      <c r="B45" s="41"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="56" t="s">
+      <c r="A45" s="51"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="61"/>
+      <c r="F45" s="61"/>
+      <c r="G45" s="62"/>
+      <c r="H45" s="16"/>
+    </row>
+    <row r="46" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A46" s="51"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="62"/>
+      <c r="H46" s="16"/>
+    </row>
+    <row r="47" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A47" s="51"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="E45" s="57"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="26"/>
-    </row>
-    <row r="46" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A46" s="40"/>
-      <c r="B46" s="41"/>
-      <c r="C46" s="42"/>
-      <c r="D46" s="18" t="s">
+      <c r="E47" s="66"/>
+      <c r="F47" s="67"/>
+      <c r="G47" s="68"/>
+      <c r="H47" s="69"/>
+    </row>
+    <row r="48" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A48" s="51"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="E46" s="19"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="28"/>
-    </row>
-    <row r="47" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A47" s="40"/>
-      <c r="B47" s="41"/>
-      <c r="C47" s="42"/>
-      <c r="D47" s="22" t="s">
+      <c r="E48" s="73"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="71"/>
+    </row>
+    <row r="49" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A49" s="51"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="E47" s="23"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="26"/>
-    </row>
-    <row r="48" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A48" s="40"/>
-      <c r="B48" s="41"/>
-      <c r="C48" s="42"/>
-      <c r="D48" s="18" t="s">
+      <c r="E49" s="77"/>
+      <c r="F49" s="78"/>
+      <c r="G49" s="68"/>
+      <c r="H49" s="69"/>
+    </row>
+    <row r="50" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A50" s="51"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="E48" s="19"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="28"/>
-    </row>
-    <row r="49" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A49" s="40"/>
-      <c r="B49" s="41"/>
-      <c r="C49" s="42"/>
-      <c r="D49" s="23" t="s">
+      <c r="E50" s="73"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="71"/>
+    </row>
+    <row r="51" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A51" s="51"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="E49" s="23"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="25"/>
-      <c r="H49" s="26"/>
-    </row>
-    <row r="50" spans="1:8" ht="10.75" customHeight="1" thickBot="1">
-      <c r="A50" s="43"/>
-      <c r="B50" s="44"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="31" t="s">
+      <c r="E51" s="77"/>
+      <c r="F51" s="78"/>
+      <c r="G51" s="68"/>
+      <c r="H51" s="69"/>
+    </row>
+    <row r="52" spans="1:8" ht="10.75" customHeight="1" thickBot="1">
+      <c r="A52" s="54"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="E50" s="32"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="30"/>
-    </row>
-    <row r="51" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F51" s="21" t="s">
+      <c r="E52" s="82"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="79"/>
+      <c r="H52" s="80"/>
+    </row>
+    <row r="53" spans="1:8" ht="9" customHeight="1" thickTop="1">
+      <c r="F53" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-    </row>
-    <row r="52" spans="1:8" ht="9" customHeight="1">
-      <c r="A52"/>
-      <c r="B52"/>
-      <c r="C52"/>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52"/>
-      <c r="G52"/>
-      <c r="H52"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53"/>
-      <c r="B53"/>
-      <c r="C53"/>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="H53"/>
-    </row>
-    <row r="54" spans="1:8">
+      <c r="G53" s="75"/>
+      <c r="H53" s="75"/>
+    </row>
+    <row r="54" spans="1:8" ht="9" customHeight="1">
       <c r="A54"/>
       <c r="B54"/>
       <c r="C54"/>
@@ -1996,53 +2027,39 @@
       <c r="G59"/>
       <c r="H59"/>
     </row>
+    <row r="60" spans="1:8">
+      <c r="A60"/>
+      <c r="B60"/>
+      <c r="C60"/>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60"/>
+      <c r="G60"/>
+      <c r="H60"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61"/>
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="H61"/>
+    </row>
   </sheetData>
-  <mergeCells count="64">
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A6:A18"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="K12:K22"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="K23:K30"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="A19:A26"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A33:C50"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D35:G35"/>
+  <mergeCells count="68">
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="G51:H52"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A35:C52"/>
+    <mergeCell ref="D35:H35"/>
     <mergeCell ref="D36:G36"/>
     <mergeCell ref="D37:G37"/>
     <mergeCell ref="D38:G38"/>
@@ -2052,16 +2069,54 @@
     <mergeCell ref="D42:G42"/>
     <mergeCell ref="D43:G43"/>
     <mergeCell ref="D44:G44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="G45:H46"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D46:G46"/>
     <mergeCell ref="D47:F47"/>
     <mergeCell ref="G47:H48"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="K25:K32"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="A21:A28"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="K14:K24"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="A8:A20"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.195138888888889" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/refrigerasi.xlsx
+++ b/public/assets/templates/maintenance/refrigerasi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8502E5CA-AFC8-42F9-8C73-F862A582E721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CBDF79-C733-4D97-B395-6A8657142FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{BD070262-A742-4FD6-B71B-7736A1293F38}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
   <si>
     <t>LAPORAN MAINTENANCE REFRIGERASI</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t xml:space="preserve">: </t>
+  </si>
+  <si>
+    <t>MID</t>
   </si>
 </sst>
 </file>
@@ -274,7 +277,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -531,19 +534,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -676,7 +666,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -731,6 +721,153 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -764,170 +901,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1311,28 +1289,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickTop="1">
-      <c r="A1" s="21"/>
-      <c r="B1" s="22"/>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="70"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="23"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="27" t="s">
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="28"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="77"/>
     </row>
     <row r="3" spans="1:11" ht="10.75" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -1342,15 +1320,15 @@
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19" t="s">
+      <c r="E3" s="67"/>
+      <c r="F3" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="19"/>
-      <c r="H3" s="20"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="69"/>
     </row>
     <row r="4" spans="1:11" ht="10.75" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1360,15 +1338,15 @@
         <v>2</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19" t="s">
+      <c r="E4" s="67"/>
+      <c r="F4" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="20"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
     </row>
     <row r="5" spans="1:11" ht="10.75" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -1378,15 +1356,15 @@
         <v>2</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="19" t="s">
+      <c r="E5" s="67"/>
+      <c r="F5" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="20"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="69"/>
     </row>
     <row r="6" spans="1:11" ht="10.75" customHeight="1">
       <c r="A6" s="1" t="s">
@@ -1396,36 +1374,36 @@
         <v>2</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19" t="s">
+      <c r="E6" s="67"/>
+      <c r="F6" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="69"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="10.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="64"/>
       <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="65"/>
     </row>
     <row r="8" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="66" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="6"/>
@@ -1433,160 +1411,160 @@
         <v>12</v>
       </c>
       <c r="D8" s="8"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="55"/>
     </row>
     <row r="9" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A9" s="33"/>
+      <c r="A9" s="66"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="8"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="35"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A10" s="33"/>
+      <c r="A10" s="66"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="8"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="35"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="55"/>
     </row>
     <row r="11" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A11" s="33"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="55"/>
     </row>
     <row r="12" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A12" s="33"/>
+      <c r="A12" s="66"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="8"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="35"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="55"/>
     </row>
     <row r="13" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A13" s="33"/>
+      <c r="A13" s="66"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="8"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="35"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="55"/>
     </row>
     <row r="14" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A14" s="33"/>
+      <c r="A14" s="66"/>
       <c r="B14" s="6"/>
       <c r="C14" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="8"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="35"/>
-      <c r="K14" s="36"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="55"/>
+      <c r="K14" s="63"/>
     </row>
     <row r="15" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A15" s="33"/>
+      <c r="A15" s="66"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="8"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="35"/>
-      <c r="K15" s="36"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="55"/>
+      <c r="K15" s="63"/>
     </row>
     <row r="16" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A16" s="33"/>
+      <c r="A16" s="66"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="8"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="35"/>
-      <c r="K16" s="36"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="55"/>
+      <c r="K16" s="63"/>
     </row>
     <row r="17" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A17" s="33"/>
+      <c r="A17" s="66"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="8"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="35"/>
-      <c r="K17" s="36"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="55"/>
+      <c r="K17" s="63"/>
     </row>
     <row r="18" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A18" s="33"/>
+      <c r="A18" s="66"/>
       <c r="B18" s="6"/>
       <c r="C18" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D18" s="8"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="35"/>
-      <c r="K18" s="36"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="55"/>
+      <c r="K18" s="63"/>
     </row>
     <row r="19" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A19" s="33"/>
+      <c r="A19" s="66"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="35"/>
-      <c r="K19" s="36"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="55"/>
+      <c r="K19" s="63"/>
     </row>
     <row r="20" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A20" s="33"/>
+      <c r="A20" s="66"/>
       <c r="B20" s="6"/>
       <c r="C20" s="11"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="35"/>
-      <c r="K20" s="36"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="55"/>
+      <c r="K20" s="63"/>
     </row>
     <row r="21" spans="1:11" s="12" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="62" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="6"/>
@@ -1594,101 +1572,101 @@
         <v>24</v>
       </c>
       <c r="D21" s="8"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="35"/>
-      <c r="K21" s="36"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="55"/>
+      <c r="K21" s="63"/>
     </row>
     <row r="22" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A22" s="44"/>
+      <c r="A22" s="62"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="8"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="35"/>
-      <c r="K22" s="36"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="55"/>
+      <c r="K22" s="63"/>
     </row>
     <row r="23" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A23" s="44"/>
+      <c r="A23" s="62"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D23" s="8"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="35"/>
-      <c r="K23" s="36"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="55"/>
+      <c r="K23" s="63"/>
     </row>
     <row r="24" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A24" s="44"/>
+      <c r="A24" s="62"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D24" s="8"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="35"/>
-      <c r="K24" s="36"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="55"/>
+      <c r="K24" s="63"/>
     </row>
     <row r="25" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A25" s="44"/>
+      <c r="A25" s="62"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="8"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="35"/>
-      <c r="K25" s="37"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="55"/>
+      <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A26" s="44"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="8"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="35"/>
-      <c r="K26" s="37"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="55"/>
+      <c r="K26" s="53"/>
     </row>
     <row r="27" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A27" s="44"/>
+      <c r="A27" s="62"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
       <c r="D27" s="8"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="35"/>
-      <c r="K27" s="37"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="55"/>
+      <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A28" s="44"/>
+      <c r="A28" s="62"/>
       <c r="B28" s="6"/>
       <c r="C28" s="11"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="35"/>
-      <c r="K28" s="37"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="55"/>
+      <c r="K28" s="53"/>
     </row>
     <row r="29" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A29" s="38" t="s">
+      <c r="A29" s="56" t="s">
         <v>29</v>
       </c>
       <c r="B29" s="6"/>
@@ -1696,276 +1674,278 @@
         <v>30</v>
       </c>
       <c r="D29" s="8"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="43"/>
-      <c r="K29" s="37"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="61"/>
+      <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A30" s="39"/>
+      <c r="A30" s="57"/>
       <c r="B30" s="6"/>
       <c r="C30" s="13" t="s">
         <v>31</v>
       </c>
       <c r="D30" s="8"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="43"/>
-      <c r="K30" s="37"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="61"/>
+      <c r="K30" s="53"/>
     </row>
     <row r="31" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A31" s="39"/>
+      <c r="A31" s="57"/>
       <c r="B31" s="6"/>
       <c r="C31" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D31" s="8"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="43"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="61"/>
       <c r="J31" s="14"/>
-      <c r="K31" s="37"/>
+      <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A32" s="39"/>
+      <c r="A32" s="57"/>
       <c r="B32" s="6"/>
       <c r="C32" s="10"/>
       <c r="D32" s="8"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="43"/>
-      <c r="K32" s="37"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="61"/>
+      <c r="K32" s="53"/>
     </row>
     <row r="33" spans="1:8" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A33" s="40"/>
+      <c r="A33" s="58"/>
       <c r="B33" s="6"/>
       <c r="C33" s="10"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="43"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="60"/>
+      <c r="H33" s="61"/>
     </row>
     <row r="34" spans="1:8" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A34" s="45"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="47"/>
+      <c r="A34" s="34"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="36"/>
     </row>
     <row r="35" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A35" s="48" t="s">
+      <c r="A35" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="49"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="57" t="s">
+      <c r="B35" s="38"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="58"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="47"/>
     </row>
     <row r="36" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A36" s="51"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="53"/>
-      <c r="D36" s="30" t="s">
+      <c r="A36" s="40"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="78" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="78"/>
+      <c r="F36" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="59"/>
+      <c r="G36" s="78"/>
       <c r="H36" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A37" s="51"/>
-      <c r="B37" s="52"/>
-      <c r="C37" s="53"/>
-      <c r="D37" s="60"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="62"/>
+      <c r="A37" s="40"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="78"/>
+      <c r="G37" s="78"/>
       <c r="H37" s="15"/>
     </row>
     <row r="38" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A38" s="51"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="53"/>
-      <c r="D38" s="60"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="62"/>
+      <c r="A38" s="40"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="79"/>
+      <c r="F38" s="78"/>
+      <c r="G38" s="78"/>
       <c r="H38" s="15"/>
     </row>
     <row r="39" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A39" s="51"/>
-      <c r="B39" s="52"/>
-      <c r="C39" s="53"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="62"/>
+      <c r="A39" s="40"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
       <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A40" s="51"/>
-      <c r="B40" s="52"/>
-      <c r="C40" s="53"/>
-      <c r="D40" s="60"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="62"/>
+      <c r="A40" s="40"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="79"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
       <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A41" s="51"/>
-      <c r="B41" s="52"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="62"/>
+      <c r="A41" s="40"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="79"/>
+      <c r="E41" s="79"/>
+      <c r="F41" s="78"/>
+      <c r="G41" s="78"/>
       <c r="H41" s="16"/>
     </row>
     <row r="42" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A42" s="51"/>
-      <c r="B42" s="52"/>
-      <c r="C42" s="53"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="62"/>
+      <c r="A42" s="40"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="79"/>
+      <c r="E42" s="79"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="78"/>
       <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A43" s="51"/>
-      <c r="B43" s="52"/>
-      <c r="C43" s="53"/>
-      <c r="D43" s="60"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="61"/>
-      <c r="G43" s="62"/>
+      <c r="A43" s="40"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="79"/>
+      <c r="E43" s="79"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="78"/>
       <c r="H43" s="16"/>
     </row>
     <row r="44" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A44" s="51"/>
-      <c r="B44" s="52"/>
-      <c r="C44" s="53"/>
-      <c r="D44" s="60"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="62"/>
+      <c r="A44" s="40"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="79"/>
+      <c r="E44" s="79"/>
+      <c r="F44" s="78"/>
+      <c r="G44" s="78"/>
       <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A45" s="51"/>
-      <c r="B45" s="52"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="60"/>
-      <c r="E45" s="61"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="62"/>
+      <c r="A45" s="40"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="79"/>
+      <c r="E45" s="79"/>
+      <c r="F45" s="78"/>
+      <c r="G45" s="78"/>
       <c r="H45" s="16"/>
     </row>
     <row r="46" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A46" s="51"/>
-      <c r="B46" s="52"/>
-      <c r="C46" s="53"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="62"/>
+      <c r="A46" s="40"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="79"/>
+      <c r="E46" s="79"/>
+      <c r="F46" s="78"/>
+      <c r="G46" s="78"/>
       <c r="H46" s="16"/>
     </row>
     <row r="47" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A47" s="51"/>
-      <c r="B47" s="52"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="65" t="s">
+      <c r="A47" s="40"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="E47" s="66"/>
-      <c r="F47" s="67"/>
-      <c r="G47" s="68"/>
-      <c r="H47" s="69"/>
+      <c r="E47" s="51"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="26"/>
     </row>
     <row r="48" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A48" s="51"/>
-      <c r="B48" s="52"/>
-      <c r="C48" s="53"/>
-      <c r="D48" s="72" t="s">
+      <c r="A48" s="40"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E48" s="73"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="71"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="28"/>
     </row>
     <row r="49" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A49" s="51"/>
-      <c r="B49" s="52"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="76" t="s">
+      <c r="A49" s="40"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="E49" s="77"/>
-      <c r="F49" s="78"/>
-      <c r="G49" s="68"/>
-      <c r="H49" s="69"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="26"/>
     </row>
     <row r="50" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A50" s="51"/>
-      <c r="B50" s="52"/>
-      <c r="C50" s="53"/>
-      <c r="D50" s="72" t="s">
+      <c r="A50" s="40"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="E50" s="73"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="70"/>
-      <c r="H50" s="71"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="28"/>
     </row>
     <row r="51" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A51" s="51"/>
-      <c r="B51" s="52"/>
-      <c r="C51" s="53"/>
-      <c r="D51" s="77" t="s">
+      <c r="A51" s="40"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="42"/>
+      <c r="D51" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E51" s="77"/>
-      <c r="F51" s="78"/>
-      <c r="G51" s="68"/>
-      <c r="H51" s="69"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="26"/>
     </row>
     <row r="52" spans="1:8" ht="10.75" customHeight="1" thickBot="1">
-      <c r="A52" s="54"/>
-      <c r="B52" s="55"/>
-      <c r="C52" s="56"/>
-      <c r="D52" s="81" t="s">
+      <c r="A52" s="43"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="E52" s="82"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="79"/>
-      <c r="H52" s="80"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="33"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="30"/>
     </row>
     <row r="53" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F53" s="75" t="s">
+      <c r="F53" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="G53" s="75"/>
-      <c r="H53" s="75"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
     </row>
     <row r="54" spans="1:8" ht="9" customHeight="1">
       <c r="A54"/>
@@ -2048,31 +2028,57 @@
       <c r="H61"/>
     </row>
   </sheetData>
-  <mergeCells count="68">
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="G51:H52"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A35:C52"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="D38:G38"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D43:G43"/>
-    <mergeCell ref="D44:G44"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D46:G46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="G47:H48"/>
+  <mergeCells count="79">
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="A8:A20"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="K14:K24"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E20:H20"/>
     <mergeCell ref="K25:K32"/>
     <mergeCell ref="E26:H26"/>
     <mergeCell ref="E27:H27"/>
@@ -2089,34 +2095,19 @@
     <mergeCell ref="E23:H23"/>
     <mergeCell ref="E24:H24"/>
     <mergeCell ref="E25:H25"/>
-    <mergeCell ref="K14:K24"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="A8:A20"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A35:C52"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="G47:H48"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="G51:H52"/>
+    <mergeCell ref="D52:F52"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.195138888888889" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/refrigerasi.xlsx
+++ b/public/assets/templates/maintenance/refrigerasi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CBDF79-C733-4D97-B395-6A8657142FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C6BE6F-E336-472F-BDB6-79CDDF9EB8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{BD070262-A742-4FD6-B71B-7736A1293F38}"/>
   </bookViews>
@@ -147,18 +147,9 @@
     <t>Teknisi</t>
   </si>
   <si>
-    <t>Diketahui : Miftah Hasan Fuadi</t>
-  </si>
-  <si>
     <t>Staff Engineering</t>
   </si>
   <si>
-    <t>Diterima</t>
-  </si>
-  <si>
-    <t>Staff User</t>
-  </si>
-  <si>
     <t>FRM/EUT/01/009/005-02</t>
   </si>
   <si>
@@ -181,13 +172,22 @@
   </si>
   <si>
     <t>MID</t>
+  </si>
+  <si>
+    <t>Diketahui : Reja Firmansyah</t>
+  </si>
+  <si>
+    <t>Supervisor Engineering</t>
+  </si>
+  <si>
+    <t>Diperiksa : Miftah Hasan Fuadi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,63 +196,77 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="7"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -260,7 +274,7 @@
       <sz val="7"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -598,15 +612,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color auto="1"/>
       </left>
@@ -659,157 +664,195 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -817,99 +860,77 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{FA9545F1-4E65-4EA6-B8F6-D4D9544F2E01}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{CBA2221F-BF44-4F38-BFDC-F624C106B5A3}"/>
     <cellStyle name="Normal_Inspection Test Plan" xfId="1" xr:uid="{F4590EEB-F6C3-4689-ADD4-09A7789E93CD}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1289,82 +1310,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickTop="1">
-      <c r="A1" s="70"/>
-      <c r="B1" s="71"/>
-      <c r="C1" s="74" t="s">
+      <c r="A1" s="68"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="73"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="76" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="77"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:11" ht="10.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="67"/>
-      <c r="F3" s="68" t="s">
+      <c r="E3" s="65"/>
+      <c r="F3" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="68"/>
-      <c r="H3" s="69"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="67"/>
     </row>
     <row r="4" spans="1:11" ht="10.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="67" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="68"/>
-      <c r="H4" s="69"/>
+      <c r="D4" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="65"/>
+      <c r="F4" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="66"/>
+      <c r="H4" s="67"/>
     </row>
     <row r="5" spans="1:11" ht="10.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="67" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="67"/>
-      <c r="F5" s="68" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="68"/>
-      <c r="H5" s="69"/>
+      <c r="D5" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="65"/>
+      <c r="F5" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="66"/>
+      <c r="H5" s="67"/>
     </row>
     <row r="6" spans="1:11" ht="10.75" customHeight="1">
       <c r="A6" s="1" t="s">
@@ -1374,36 +1395,36 @@
         <v>2</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="67" t="s">
+      <c r="D6" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="67"/>
-      <c r="F6" s="68" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="68"/>
-      <c r="H6" s="69"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="67"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="10.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="64"/>
+      <c r="C7" s="60"/>
       <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="65"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="63"/>
     </row>
     <row r="8" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A8" s="66" t="s">
+      <c r="A8" s="64" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="6"/>
@@ -1411,160 +1432,160 @@
         <v>12</v>
       </c>
       <c r="D8" s="8"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="55"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="51"/>
     </row>
     <row r="9" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A9" s="66"/>
+      <c r="A9" s="64"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="8"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="55"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="51"/>
     </row>
     <row r="10" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A10" s="66"/>
+      <c r="A10" s="64"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="8"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="55"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="51"/>
     </row>
     <row r="11" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A11" s="66"/>
+      <c r="A11" s="64"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="55"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="51"/>
     </row>
     <row r="12" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A12" s="66"/>
+      <c r="A12" s="64"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="8"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="55"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="51"/>
     </row>
     <row r="13" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A13" s="66"/>
+      <c r="A13" s="64"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="8"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="55"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="51"/>
     </row>
     <row r="14" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A14" s="66"/>
+      <c r="A14" s="64"/>
       <c r="B14" s="6"/>
       <c r="C14" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="8"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="55"/>
-      <c r="K14" s="63"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="51"/>
+      <c r="K14" s="59"/>
     </row>
     <row r="15" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A15" s="66"/>
+      <c r="A15" s="64"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="8"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="55"/>
-      <c r="K15" s="63"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="51"/>
+      <c r="K15" s="59"/>
     </row>
     <row r="16" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A16" s="66"/>
+      <c r="A16" s="64"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="8"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="55"/>
-      <c r="K16" s="63"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="51"/>
+      <c r="K16" s="59"/>
     </row>
     <row r="17" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A17" s="66"/>
+      <c r="A17" s="64"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="8"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="55"/>
-      <c r="K17" s="63"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="51"/>
+      <c r="K17" s="59"/>
     </row>
     <row r="18" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A18" s="66"/>
+      <c r="A18" s="64"/>
       <c r="B18" s="6"/>
       <c r="C18" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D18" s="8"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="55"/>
-      <c r="K18" s="63"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="51"/>
+      <c r="K18" s="59"/>
     </row>
     <row r="19" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A19" s="66"/>
+      <c r="A19" s="64"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="55"/>
-      <c r="K19" s="63"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="51"/>
+      <c r="K19" s="59"/>
     </row>
     <row r="20" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A20" s="66"/>
+      <c r="A20" s="64"/>
       <c r="B20" s="6"/>
       <c r="C20" s="11"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="55"/>
-      <c r="K20" s="63"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="51"/>
+      <c r="K20" s="59"/>
     </row>
     <row r="21" spans="1:11" s="12" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A21" s="62" t="s">
+      <c r="A21" s="58" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="6"/>
@@ -1572,101 +1593,101 @@
         <v>24</v>
       </c>
       <c r="D21" s="8"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="55"/>
-      <c r="K21" s="63"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="51"/>
+      <c r="K21" s="59"/>
     </row>
     <row r="22" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A22" s="62"/>
+      <c r="A22" s="58"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="8"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="55"/>
-      <c r="K22" s="63"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="51"/>
+      <c r="K22" s="59"/>
     </row>
     <row r="23" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A23" s="62"/>
+      <c r="A23" s="58"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D23" s="8"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="55"/>
-      <c r="K23" s="63"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="51"/>
+      <c r="K23" s="59"/>
     </row>
     <row r="24" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A24" s="62"/>
+      <c r="A24" s="58"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D24" s="8"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="55"/>
-      <c r="K24" s="63"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="51"/>
+      <c r="K24" s="59"/>
     </row>
     <row r="25" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A25" s="62"/>
+      <c r="A25" s="58"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="8"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="55"/>
-      <c r="K25" s="53"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="51"/>
+      <c r="K25" s="49"/>
     </row>
     <row r="26" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A26" s="62"/>
+      <c r="A26" s="58"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="8"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="55"/>
-      <c r="K26" s="53"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="51"/>
+      <c r="K26" s="49"/>
     </row>
     <row r="27" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A27" s="62"/>
+      <c r="A27" s="58"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
       <c r="D27" s="8"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="55"/>
-      <c r="K27" s="53"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="51"/>
+      <c r="K27" s="49"/>
     </row>
     <row r="28" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A28" s="62"/>
+      <c r="A28" s="58"/>
       <c r="B28" s="6"/>
       <c r="C28" s="11"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="55"/>
-      <c r="K28" s="53"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="51"/>
+      <c r="K28" s="49"/>
     </row>
     <row r="29" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A29" s="56" t="s">
+      <c r="A29" s="52" t="s">
         <v>29</v>
       </c>
       <c r="B29" s="6"/>
@@ -1674,278 +1695,278 @@
         <v>30</v>
       </c>
       <c r="D29" s="8"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="61"/>
-      <c r="K29" s="53"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="57"/>
+      <c r="K29" s="49"/>
     </row>
     <row r="30" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A30" s="57"/>
+      <c r="A30" s="53"/>
       <c r="B30" s="6"/>
       <c r="C30" s="13" t="s">
         <v>31</v>
       </c>
       <c r="D30" s="8"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="60"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="61"/>
-      <c r="K30" s="53"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="57"/>
+      <c r="K30" s="49"/>
     </row>
     <row r="31" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A31" s="57"/>
+      <c r="A31" s="53"/>
       <c r="B31" s="6"/>
       <c r="C31" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D31" s="8"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="61"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="57"/>
       <c r="J31" s="14"/>
-      <c r="K31" s="53"/>
+      <c r="K31" s="49"/>
     </row>
     <row r="32" spans="1:11" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A32" s="57"/>
+      <c r="A32" s="53"/>
       <c r="B32" s="6"/>
       <c r="C32" s="10"/>
       <c r="D32" s="8"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="61"/>
-      <c r="K32" s="53"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="57"/>
+      <c r="K32" s="49"/>
     </row>
     <row r="33" spans="1:8" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A33" s="58"/>
+      <c r="A33" s="54"/>
       <c r="B33" s="6"/>
       <c r="C33" s="10"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="59"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="61"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="57"/>
     </row>
     <row r="34" spans="1:8" s="9" customFormat="1" ht="10.75" customHeight="1">
-      <c r="A34" s="34"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="36"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="34"/>
     </row>
     <row r="35" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A35" s="37" t="s">
+      <c r="A35" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="38"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="46" t="s">
+      <c r="B35" s="36"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="47"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="45"/>
     </row>
     <row r="36" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A36" s="40"/>
-      <c r="B36" s="41"/>
-      <c r="C36" s="42"/>
-      <c r="D36" s="78" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" s="78"/>
-      <c r="F36" s="78" t="s">
+      <c r="A36" s="38"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="G36" s="78"/>
+      <c r="G36" s="76"/>
       <c r="H36" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A37" s="40"/>
-      <c r="B37" s="41"/>
-      <c r="C37" s="42"/>
-      <c r="D37" s="79"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="78"/>
-      <c r="G37" s="78"/>
+      <c r="A37" s="38"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
       <c r="H37" s="15"/>
     </row>
     <row r="38" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A38" s="40"/>
-      <c r="B38" s="41"/>
-      <c r="C38" s="42"/>
-      <c r="D38" s="79"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="78"/>
-      <c r="G38" s="78"/>
+      <c r="A38" s="38"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
       <c r="H38" s="15"/>
     </row>
     <row r="39" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A39" s="40"/>
-      <c r="B39" s="41"/>
-      <c r="C39" s="42"/>
-      <c r="D39" s="79"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="78"/>
-      <c r="G39" s="78"/>
+      <c r="A39" s="38"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
       <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A40" s="40"/>
-      <c r="B40" s="41"/>
-      <c r="C40" s="42"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="78"/>
+      <c r="A40" s="38"/>
+      <c r="B40" s="39"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
       <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A41" s="40"/>
-      <c r="B41" s="41"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="79"/>
-      <c r="E41" s="79"/>
-      <c r="F41" s="78"/>
-      <c r="G41" s="78"/>
+      <c r="A41" s="38"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="77"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
       <c r="H41" s="16"/>
     </row>
     <row r="42" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A42" s="40"/>
-      <c r="B42" s="41"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="79"/>
-      <c r="E42" s="79"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="78"/>
+      <c r="A42" s="38"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
       <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A43" s="40"/>
-      <c r="B43" s="41"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="79"/>
-      <c r="E43" s="79"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="78"/>
+      <c r="A43" s="38"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="77"/>
+      <c r="E43" s="77"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
       <c r="H43" s="16"/>
     </row>
     <row r="44" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A44" s="40"/>
-      <c r="B44" s="41"/>
-      <c r="C44" s="42"/>
-      <c r="D44" s="79"/>
-      <c r="E44" s="79"/>
-      <c r="F44" s="78"/>
-      <c r="G44" s="78"/>
+      <c r="A44" s="38"/>
+      <c r="B44" s="39"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="77"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
       <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A45" s="40"/>
-      <c r="B45" s="41"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="79"/>
-      <c r="E45" s="79"/>
-      <c r="F45" s="78"/>
-      <c r="G45" s="78"/>
+      <c r="A45" s="38"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="77"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="76"/>
       <c r="H45" s="16"/>
     </row>
     <row r="46" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A46" s="40"/>
-      <c r="B46" s="41"/>
-      <c r="C46" s="42"/>
-      <c r="D46" s="79"/>
-      <c r="E46" s="79"/>
-      <c r="F46" s="78"/>
-      <c r="G46" s="78"/>
+      <c r="A46" s="38"/>
+      <c r="B46" s="39"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="77"/>
+      <c r="E46" s="77"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="76"/>
       <c r="H46" s="16"/>
     </row>
     <row r="47" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A47" s="40"/>
-      <c r="B47" s="41"/>
-      <c r="C47" s="42"/>
-      <c r="D47" s="50" t="s">
+      <c r="A47" s="38"/>
+      <c r="B47" s="39"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="E47" s="51"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="26"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="20"/>
     </row>
     <row r="48" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A48" s="40"/>
-      <c r="B48" s="41"/>
-      <c r="C48" s="42"/>
-      <c r="D48" s="18" t="s">
+      <c r="A48" s="38"/>
+      <c r="B48" s="39"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E48" s="19"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="28"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="21"/>
+      <c r="H48" s="22"/>
     </row>
     <row r="49" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A49" s="40"/>
-      <c r="B49" s="41"/>
-      <c r="C49" s="42"/>
-      <c r="D49" s="22" t="s">
+      <c r="A49" s="38"/>
+      <c r="B49" s="39"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="78" t="s">
+        <v>50</v>
+      </c>
+      <c r="E49" s="78"/>
+      <c r="F49" s="78"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="20"/>
+    </row>
+    <row r="50" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A50" s="38"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E49" s="23"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="25"/>
-      <c r="H49" s="26"/>
-    </row>
-    <row r="50" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A50" s="40"/>
-      <c r="B50" s="41"/>
-      <c r="C50" s="42"/>
-      <c r="D50" s="18" t="s">
+      <c r="E50" s="24"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="21"/>
+      <c r="H50" s="22"/>
+    </row>
+    <row r="51" spans="1:8" ht="10.75" customHeight="1">
+      <c r="A51" s="38"/>
+      <c r="B51" s="39"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="20"/>
+    </row>
+    <row r="52" spans="1:8" ht="10.75" customHeight="1" thickBot="1">
+      <c r="A52" s="41"/>
+      <c r="B52" s="42"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E52" s="30"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="27"/>
+    </row>
+    <row r="53" spans="1:8" ht="9" customHeight="1" thickTop="1">
+      <c r="F53" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="E50" s="19"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="28"/>
-    </row>
-    <row r="51" spans="1:8" ht="10.75" customHeight="1">
-      <c r="A51" s="40"/>
-      <c r="B51" s="41"/>
-      <c r="C51" s="42"/>
-      <c r="D51" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="E51" s="23"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="25"/>
-      <c r="H51" s="26"/>
-    </row>
-    <row r="52" spans="1:8" ht="10.75" customHeight="1" thickBot="1">
-      <c r="A52" s="43"/>
-      <c r="B52" s="44"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="E52" s="32"/>
-      <c r="F52" s="33"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="30"/>
-    </row>
-    <row r="53" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F53" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
     </row>
     <row r="54" spans="1:8" ht="9" customHeight="1">
       <c r="A54"/>
@@ -2029,15 +2050,6 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D43:E43"/>
     <mergeCell ref="D44:E44"/>
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="D46:E46"/>
@@ -2045,12 +2057,12 @@
     <mergeCell ref="F42:G42"/>
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D43:E43"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="A1:B2"/>
@@ -2101,12 +2113,21 @@
     <mergeCell ref="D47:F47"/>
     <mergeCell ref="G47:H48"/>
     <mergeCell ref="D48:F48"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
     <mergeCell ref="F53:H53"/>
-    <mergeCell ref="D49:F49"/>
     <mergeCell ref="G49:H50"/>
     <mergeCell ref="D50:F50"/>
+    <mergeCell ref="G51:H52"/>
     <mergeCell ref="D51:F51"/>
-    <mergeCell ref="G51:H52"/>
     <mergeCell ref="D52:F52"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
